--- a/www/download/IND.gross_output.s.us.rpPE.xlsx
+++ b/www/download/IND.gross_output.s.us.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>752494.98168</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>829399.27125</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>832678.26478</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>752129.87266</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>815120.20972</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>781105.49249</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>735918.42278</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>818548.85189</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1043916.75928</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1274561.85401</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1413363.26662</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1511399.28909</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.821</t>
+          <t>1821221.24465</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>2017526.35779</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>1968895.58857</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>396167.78119</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>389425.34302</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>349702.38207</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>359863.73897</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>357693.89626</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331113.21482</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336888.92575</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>365545.88064</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>451468.87916</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>523577.54357</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>556508.18899</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>605744.10582</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>704248.97568</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>799375.40736</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>719449.87965</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>565662.49026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551434.48693</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>507003.8431</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>522685.70802</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523220.59463</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>492505.09565</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496622.57662</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>526176.36293</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>637060.47889</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>745492.87068</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>783492.97772</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>848835.80683</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>978761.05105</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1103399.79032</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>972907.41524</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28401.43623</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30820.60983</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24225.98663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25554.54324</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25628.093</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25699.58624</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27780.08002</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31008.8956</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40492.17933</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51515.12221</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59695.11906</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71335.35282</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92537.04128</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110695.73757</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106237.58348</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>1261526.44119</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1366247.23366</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1420617.91803</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1380365.38991</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>969896.04007</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1096554.37795</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>948116.04885</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>897641.136</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>978595.75461</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1175437.15757</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1562385.44245</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1895074.57938</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.377</t>
+          <t>2377320.84208</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>2894929.56407</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>2741154.20109</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1026040.00237</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1080145.52527</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1130851.85394</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1099419.52822</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1188394.5984</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1332236.76032</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>1314026.785</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>1335753.48033</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1569015.20584</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>1798475.86541</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2.047</t>
+          <t>2047279.31899</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2.297</t>
+          <t>2296688.91947</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.536</t>
+          <t>2536378.0898</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>2697549.842</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.393</t>
+          <t>2392609.67465</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1888818.00833</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.229</t>
+          <t>2229366.1548</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.481</t>
+          <t>2480754.93414</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>2647916.15531</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>2814386.86818</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>3125236.69535</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>3454251.82819</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.794</t>
+          <t>3794147.41702</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.458</t>
+          <t>4457621.02152</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.373</t>
+          <t>5372763.54888</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6.527</t>
+          <t>6527489.8572</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>8160175.32311</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10.741</t>
+          <t>10740914.89603</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>13.913</t>
+          <t>13913136.42324</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15149964.83865</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13745.56817</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14025.103</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13541.08615</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14456.44642</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14904.16569</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14176.64369</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14825.93409</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16295.25573</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20252.26861</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23628.63618</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25577.21377</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28109.62515</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33700.83554</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40127.54318</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37463.21071</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131930.33656</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145588.42367</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138889.0318</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148099.64303</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141552.28303</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139960.6931</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154545.02045</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185157.89271</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226745.6239</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>275233.32295</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>310792.53065</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368770.01749</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456657.19042</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>564946.54779</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>458086.21635</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4289714.99955</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.148</t>
+          <t>4148350.8472</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.708</t>
+          <t>3708413.41752</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.767</t>
+          <t>3767286.13336</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>3737973.56792</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.399</t>
+          <t>3399402.20853</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>3373850.6568</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.535</t>
+          <t>3534860.73441</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>4292179.88478</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.871</t>
+          <t>4871137.04873</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>5034337.63434</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.362</t>
+          <t>5362002.02775</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>6161850.08853</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6.788</t>
+          <t>6788492.30254</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>5.914</t>
+          <t>5913505.46421</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>298365.88747</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>300756.85585</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278356.72166</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>283172.60081</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>285252.09168</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>269250.11318</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273930.34712</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>295493.52028</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>357987.64963</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>410428.67847</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444056.31049</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>484097.74638</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>561740.27321</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>630254.4631</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>549075.19184</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1137233.09765</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1180804.65846</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.085</t>
+          <t>1084757.01577</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1131351.21011</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1157813.60464</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1103652.15177</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1159249.44985</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1325268.7549</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.695</t>
+          <t>1695348.59695</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2010355.01228</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>2200858.88681</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>2435198.48464</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2.839</t>
+          <t>2838946.82881</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>3191602.43002</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>2909046.49266</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8283.83643</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9788.73997</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10859.83237</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12316.32551</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12179.36035</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12772.51023</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14048.57844</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16424.78141</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21205.70703</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26063.58469</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30167.77286</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35532.43521</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44246.99087</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48445.03863</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37266.24415</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239854.6551</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237907.01329</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229104.75534</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240112.3178</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241264.06981</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235411.79038</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233919.97869</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252336.19007</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>306651.34026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>357016.69779</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>377278.29372</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>413452.74915</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487841.7983</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552253.05822</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>469673.77601</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>2756128.53911</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2730003.4097</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.477</t>
+          <t>2476918.08085</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2560238.46343</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2562027.48929</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2414855.70244</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.445</t>
+          <t>2444529.532</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2639684.87457</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3.218</t>
+          <t>3217567.05325</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3.699</t>
+          <t>3699465.40247</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3.873</t>
+          <t>3873089.74045</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4.126</t>
+          <t>4125988.15742</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>4.729</t>
+          <t>4729165.05439</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>5.238</t>
+          <t>5238127.73635</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4.763</t>
+          <t>4763177.36481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.101</t>
+          <t>2101260.81717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>2220947.3865</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2459925.23759</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.637</t>
+          <t>2637347.57813</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2712196.54421</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>2687524.70806</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>2668744.08914</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>2908661.31497</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>3332392.14615</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3.942</t>
+          <t>3941733.15299</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>4191589.31804</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>4487219.69286</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5139696.58206</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.909</t>
+          <t>4908990.5134</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>4002420.38558</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213345.15517</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223447.60162</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213900.888</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213400.04529</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217235.41692</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>202218.87014</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>206975.0654</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>235578.53858</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>303339.46095</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356814.39674</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374855.13439</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>407994.35689</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>478252.47301</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>537862.71926</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>489053.61632</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91385.57973</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94429.68677</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97266.8189</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101699.33222</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104654.9122</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104478.0818</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115643.71912</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138588.23325</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172524.36307</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208623.28951</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228843.61944</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242887.26422</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>293236.43547</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335691.56586</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264522.8033</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461613.99355</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>546448.71254</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559879.86354</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212809.83347</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>319134.84753</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341267.60961</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>334647.75648</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>406241.6321</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>477806.10011</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>498135.18658</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>540977.33985</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>720141.36381</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>849793.95493</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1010597.25217</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1074781.69159</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>727386.69902</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754103.19355</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>829047.77571</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>827157.17116</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866029.74744</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>902411.61575</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>925415.9909</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>982647.65615</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1159060.31364</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1371614.28394</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1610529.88414</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.853</t>
+          <t>1853051.59181</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2.341</t>
+          <t>2340827.68566</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.544</t>
+          <t>2543922.83553</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>2590618.46841</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134723.39307</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149876.90979</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164938.59555</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>178120.27518</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195301.38045</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>206241.77683</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>224824.28026</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249407.63682</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318780.68156</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>379865.20657</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>417431.60801</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>463706.59768</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550941.06294</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>561762.81601</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482054.72113</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2104988.71341</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>2324819.29448</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.224</t>
+          <t>2224223.78423</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.279</t>
+          <t>2278989.53668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>2273650.16017</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.138</t>
+          <t>2137660.35747</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2182848.1148</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>2378133.78076</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.927</t>
+          <t>2927417.2305</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3357865.69895</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3.474</t>
+          <t>3474255.19799</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3.683</t>
+          <t>3682927.63676</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>4212757.68836</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>4.619</t>
+          <t>4618580.06788</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>4.021</t>
+          <t>4020984.88656</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9.871</t>
+          <t>9871402.09181</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.653</t>
+          <t>8653218.418</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.989</t>
+          <t>7988888.18361</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.179</t>
+          <t>7179054.14357</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.074</t>
+          <t>8074125.72561</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>8689624.72806</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7.611</t>
+          <t>7611125.04837</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7.256</t>
+          <t>7256470.83011</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7.844</t>
+          <t>7844053.41652</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8.568</t>
+          <t>8567572.2029</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8.632</t>
+          <t>8631934.89718</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.377</t>
+          <t>8376839.74448</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8.489</t>
+          <t>8489190.97734</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9.696</t>
+          <t>9695796.51719</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9.388</t>
+          <t>9388243.2637</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1108509.34671</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1192915.35281</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1131548.8462</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>789859.03294</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>995264.19459</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1154386.08155</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1074724.66787</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1220729.34865</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1373053.82031</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1590214.92382</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>1913875.12857</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.185</t>
+          <t>2184540.4385</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2450518.8305</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>2409391.66177</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.087</t>
+          <t>2086877.38964</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13012.95002</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16011.72486</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17948.70002</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19579.40021</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18273.80013</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19248.7999</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20729.19991</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24205.77749</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31550.79177</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38827.22596</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45762.79956</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53512.71586</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68779.84557</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87380.2149</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63756.94838</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38211.88115</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39723.50636</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37781.09976</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41560.59266</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46884.64553</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48649.6138</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48930.65896</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52493.94368</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65341.3915</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82023.75847</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93916.11395</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113315.88882</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141769.04186</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159357.5097</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140559.4319</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9059.74019</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10317.35837</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11517.97645</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12828.85861</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13434.56323</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14948.72866</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15967.24185</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17667.63885</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21866.44317</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27839.86056</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32433.11932</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41785.92693</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57759.80196</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67537.84991</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50783.69802</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>561614.75147</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>641444.02132</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>763693.32324</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>805555.89709</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>910804.55933</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1087167.93383</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1137189.51954</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1180233.59939</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1152549.9274</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.257</t>
+          <t>1257430.74966</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1422523.06488</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1601425.62333</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>1734376.82332</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.879</t>
+          <t>1879176.9176</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1471761.90399</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6810.28788</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6759.79225</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6504.52899</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7022.21424</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7201.39947</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7612.00423</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7085.95531</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7660.96435</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9137.04683</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10679.72391</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11410.39724</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12906.4076</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15298.69514</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17266.45712</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16001.56341</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>786923.58571</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>792352.00521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>734631.79263</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>760876.52075</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>776240.22052</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>743411.19552</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762957.1837</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>821869.17178</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>997998.89929</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1135221.64746</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1195322.54689</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1281437.71187</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>1485992.00088</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1692086.32088</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1521976.41218</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264793.69278</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299043.88961</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300257.78319</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>329628.38256</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>320451.15519</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>335095.52743</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374515.27799</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384060.67339</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>424185.41114</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>509518.75332</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>603836.20512</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>695167.79525</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>883621.63806</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1111403.68187</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>865782.85723</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213812.0333</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222990.11506</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>213822.28989</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223424.66515</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225367.87645</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213234.12247</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218804.7583</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236466.93974</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286966.08772</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331001.15055</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>344211.48461</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>368347.07761</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>430233.16998</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>470095.58823</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>434233.98944</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79644.24419</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82950.2155</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76895.00852</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80843.09454</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72237.66396</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73192.59749</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78998.85387</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89452.53788</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115044.05127</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148577.15376</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188278.39696</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234079.32454</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322023.23116</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394379.72946</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312861.4044</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>611082.02965</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>742843.07242</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>748922.56241</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>585286.09149</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>338189.43534</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446231.10885</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>546151.61426</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>607506.03292</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>758702.71939</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1023619.55126</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1309048.53101</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>1701038.34165</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.259</t>
+          <t>2259263.42913</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.892</t>
+          <t>2891627.874</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>2185970.42952</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45337.56892</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50111.26536</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50817.40235</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53365.72453</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47079.18453</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49218.95513</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50782.82322</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58743.00054</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79164.32126</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95242.26689</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107692.82259</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129809.86542</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173989.93873</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222263.09264</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195303.18255</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40260.23086</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40779.67183</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39685.83759</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41536.33577</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41819.65685</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39411.53714</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40018.74467</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44922.06561</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56083.43718</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65875.94685</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70482.11437</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78329.00244</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97551.78466</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112680.84917</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95937.80408</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461976.65331</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>501511.41338</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466168.81334</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>468861.31007</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>476120.03486</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466126.22559</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>430428.36138</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466075.03516</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>573860.72027</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>666076.61884</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>694302.57719</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>753739.90604</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>880097.95041</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>949568.28984</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>757060.99647</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>382448.20652</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>412167.12829</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444490.62229</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456989.47529</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456770.98809</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>503027.80797</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>393452.21779</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>437574.62436</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568297.69543</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>720650.84726</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>888719.53974</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>979252.31131</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.201</t>
+          <t>1200909.03839</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1358920.18054</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114299.58345</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>579827.12367</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>595756.99404</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>617079.60598</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>559258.11173</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>600785.57935</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>667886.93136</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588049.75076</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>607155.39682</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642358.59517</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>738392.64111</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>795818.39608</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>837615.21176</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>900791.7699</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>945759.69106</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>810483.6867</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13.475</t>
+          <t>13475212.97756</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>14.273</t>
+          <t>14272864.33987</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>15.168</t>
+          <t>15168254.22658</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>15.986</t>
+          <t>15986187.04982</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17.016</t>
+          <t>17016289.90821</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18.305</t>
+          <t>18304783.0254</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18.576</t>
+          <t>18575525.02881</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>18.873</t>
+          <t>18873334.93361</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19.828</t>
+          <t>19828498.0708</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>21.265</t>
+          <t>21264711.10108</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23.072</t>
+          <t>23072266.03663</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24479922.10987</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>25.795</t>
+          <t>25795266.07911</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>26.565</t>
+          <t>26565031.96168</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>24.803</t>
+          <t>24802899.209</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6.003</t>
+          <t>6003296.72858969</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.424</t>
+          <t>6424492.30466808</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>6543783.60858558</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6.264</t>
+          <t>6264479.68287485</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6.334</t>
+          <t>6333545.30128171</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6.598</t>
+          <t>6598368.92172176</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6.586</t>
+          <t>6585685.88599394</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>6543553.25004621</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>7373150.32141448</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>8620444.58875593</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10.019</t>
+          <t>10018945.050815</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>11.506</t>
+          <t>11505716.776729</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>13.579</t>
+          <t>13579035.7644158</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>16.651</t>
+          <t>16651487.3993075</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>15730361.8590702</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328248</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799157</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
